--- a/Travel America/orlando-nyc-components-by-route.xlsx
+++ b/Travel America/orlando-nyc-components-by-route.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap vs NYC" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Orlando'!$A$4:$F$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'New York City'!$A$4:$E$134</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gap vs NYC'!$A$4:$C$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Orlando'!$A$4:$F$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'New York City'!$A$4:$E$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gap vs NYC'!$A$4:$C$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,14 +61,14 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="11"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="10"/>
+      <color rgb="009C0006"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -102,7 +102,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,7 +122,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,14 +152,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,21 +183,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,10 +207,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -580,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -601,7 +599,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>14 routes · 57 rendered components · RED route = more than 2 NYC components missing from Orlando · green = component also in NYC</t>
+          <t>14 routes · 103 rendered components · RED route = more than 2 NYC components missing from Orlando · green = component also in NYC</t>
         </is>
       </c>
     </row>
@@ -663,7 +661,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>RED (&gt;2 missing) — missing 9: HeroSection, PlanningIntent, WhyVisit, AttractionsHub, NeighborhoodsHub, ExperiencesHub, WhereToStay, ItinerariesPreview, DataCaptureCTA; extra: OrlandoPlanningQuiz</t>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -696,17 +694,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>HeroSection</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>./components/Hero/HeroSection</t>
         </is>
       </c>
       <c r="F7" s="11" t="n"/>
@@ -716,71 +714,63 @@
       <c r="B8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>OrlandoPlanningQuiz</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Local</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>./components/OrlandoPlanningQuiz</t>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
         </is>
       </c>
       <c r="F8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>/orlando/best-areas-to-stay</t>
-        </is>
-      </c>
+      <c r="A9" s="10" t="inlineStr"/>
       <c r="B9" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>PlanningIntent</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/header/header</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
+          <t>./components/PlanningIntent/PlanningIntent</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr"/>
       <c r="B10" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>WhyVisit</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>./components/WhyVisit/WhyVisit</t>
         </is>
       </c>
       <c r="F10" s="11" t="n"/>
@@ -788,21 +778,21 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr"/>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Banner</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>AttractionsHub</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/bestareatostay/Banner/Banner</t>
+          <t>./components/AttractionsHub/AttractionHub</t>
         </is>
       </c>
       <c r="F11" s="11" t="n"/>
@@ -810,21 +800,21 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr"/>
       <c r="B12" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>SoloTripIntro</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>NeighborhoodsHub</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/bestareatostay/solotripintro/solotripintro</t>
+          <t>./components/NeighborhoodsHub/NeighborhoodsHub</t>
         </is>
       </c>
       <c r="F12" s="11" t="n"/>
@@ -832,21 +822,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr"/>
       <c r="B13" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>SectionSafestNeighborhoods</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>ExperiencesHub</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/bestareatostay/safestneighborhood/safestneighborhood</t>
+          <t>./components/ExperiencesHub/ExperiencesHub</t>
         </is>
       </c>
       <c r="F13" s="11" t="n"/>
@@ -854,21 +844,21 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr"/>
       <c r="B14" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>NeighborhoodRankingCards</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>WhereToStay</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/neighborhoodrankingcard/neighborhoodrankingcard</t>
+          <t>./components/WhereToStay/WhereToStay</t>
         </is>
       </c>
       <c r="F14" s="11" t="n"/>
@@ -876,21 +866,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr"/>
       <c r="B15" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>ItinerariesPreview</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/faqsection/faqsection</t>
+          <t>./components/ItinerariesPreview/ItinerariesPreview</t>
         </is>
       </c>
       <c r="F15" s="11" t="n"/>
@@ -898,29 +888,29 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr"/>
       <c r="B16" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>DataCaptureCTA</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/Header/Footer/footer</t>
+          <t>./components/DataCapture/DataCaptureCTA</t>
         </is>
       </c>
       <c r="F16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>/orlando/bookings</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/best-areas-to-stay</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
@@ -928,7 +918,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>BookingClient</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -938,27 +928,23 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/booking/BookingClient</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
+          <t>@/app/components/destination/header/header</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>/orlando/food</t>
-        </is>
-      </c>
+      <c r="A18" s="10" t="inlineStr"/>
       <c r="B18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>BookingCTA</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -968,23 +954,19 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/header/header</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr"/>
       <c r="B19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>BookingCTA</t>
+          <t>Banner</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -994,7 +976,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>@/app/components/destination/bestareatostay/Banner/Banner</t>
         </is>
       </c>
       <c r="F19" s="11" t="n"/>
@@ -1002,11 +984,11 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr"/>
       <c r="B20" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>SoloTripIntro</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1016,23 +998,19 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/Header/Footer/footer</t>
+          <t>@/app/components/destination/bestareatostay/solotripintro/solotripintro</t>
         </is>
       </c>
       <c r="F20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>/orlando/group-travel</t>
-        </is>
-      </c>
+      <c r="A21" s="10" t="inlineStr"/>
       <c r="B21" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>SectionSafestNeighborhoods</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1042,23 +1020,19 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/header/header</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
+          <t>@/app/components/destination/bestareatostay/safestneighborhood/safestneighborhood</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr"/>
       <c r="B22" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>BookingCTA</t>
+          <t>NeighborhoodRankingCards</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1068,7 +1042,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>@/app/components/destination/neighborhoodrankingcard/neighborhoodrankingcard</t>
         </is>
       </c>
       <c r="F22" s="11" t="n"/>
@@ -1076,103 +1050,111 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr"/>
       <c r="B23" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/faqsection/faqsection</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr"/>
+      <c r="B24" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
           <t>Footer</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>@/app/components/Header/Footer/footer</t>
         </is>
       </c>
-      <c r="F23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>/orlando/is-orlando-safe-at-night</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
+      <c r="F24" s="11" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/bookings</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>BookingClient</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/booking/BookingClient</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/food</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>@/app/components/destination/header/header</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>RED (&gt;2 missing) — missing 10: HeroSafety, SafetyMeter, NeighborhoodSafetyGrid, ScenarioCards, CorePrinciples, TransitSafety, NeighborhoodCards, EmergencyBlock, InterlinkingGrid, TrustBlock; extra: WhyTrustThisGuide</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr"/>
-      <c r="B25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr"/>
-      <c r="B26" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>@/app/components/destination/faqsection/faqsection</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="n"/>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr"/>
       <c r="B27" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -1194,7 +1176,7 @@
     <row r="28">
       <c r="A28" s="10" t="inlineStr"/>
       <c r="B28" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
@@ -1214,9 +1196,9 @@
       <c r="F28" s="11" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>/orlando/itinerary</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/group-travel</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -1237,9 +1219,9 @@
           <t>@/app/components/destination/header/header</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>no NYC counterpart</t>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
         </is>
       </c>
     </row>
@@ -1288,9 +1270,9 @@
       <c r="F31" s="11" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>/orlando/landmark</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/is-orlando-safe-at-night</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
@@ -1311,7 +1293,7 @@
           <t>@/app/components/destination/header/header</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
@@ -1346,69 +1328,61 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>HeroSafety</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/Header/Footer/footer</t>
+          <t>./components/hero/hero</t>
         </is>
       </c>
       <c r="F34" s="11" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>/orlando/neighborhood-guide</t>
-        </is>
-      </c>
+      <c r="A35" s="10" t="inlineStr"/>
       <c r="B35" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>SafetyMeter</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/header/header</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>RED (&gt;2 missing) — missing 8: IntroSection, CityOrganization, NeighborhoodsByStyle, PopularNeighborhoods, WhereFirstTimersStay, GettingAround, SafetyOverview, NeighborhoodGuideCTA; extra: FAQAccordion, WhyTrustThisGuide</t>
-        </is>
-      </c>
+          <t>./components/SafetyMeter/SafetyMeter</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr"/>
       <c r="B36" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>NeighborhoodSafetyGrid</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>./components/NeighborhoodSafetyGrid/NeighborhoodSafetyGrid</t>
         </is>
       </c>
       <c r="F36" s="11" t="n"/>
@@ -1416,21 +1390,21 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr"/>
       <c r="B37" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>ScenarioCards</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
+          <t>./components/ScenarioCards/ScenarioCards</t>
         </is>
       </c>
       <c r="F37" s="11" t="n"/>
@@ -1438,21 +1412,21 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr"/>
       <c r="B38" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>CorePrinciples</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/faqsection/faqsection</t>
+          <t>./components/CorePrinciples/CorePrinciples</t>
         </is>
       </c>
       <c r="F38" s="11" t="n"/>
@@ -1460,73 +1434,65 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr"/>
       <c r="B39" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>TransitSafety</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/Header/Footer/footer</t>
+          <t>./components/TransitSafety/TransitSafety</t>
         </is>
       </c>
       <c r="F39" s="11" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>/orlando/orlando-female-solo-travel-guide</t>
-        </is>
-      </c>
+      <c r="A40" s="10" t="inlineStr"/>
       <c r="B40" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>NeighborhoodCards</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/header/header</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>RED (&gt;2 missing) — missing 10: Hero, InfoSection, FemaleSafetyNarrative, CoreSafetyPrinciplesGrid, ScenarioSection, ScenarioFilter, SafetySection, MicroScenarios, PackingEssentials, LinkHubGrid</t>
-        </is>
-      </c>
+          <t>./components/NeighborhoodCards/NeighborhoodCards</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr"/>
       <c r="B41" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>EmergencyBlock</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>./components/EmergencyBlock/EmergencyBlock</t>
         </is>
       </c>
       <c r="F41" s="11" t="n"/>
@@ -1534,21 +1500,21 @@
     <row r="42">
       <c r="A42" s="10" t="inlineStr"/>
       <c r="B42" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
+          <t>./components/FAQAccordion/FAQAccordion</t>
         </is>
       </c>
       <c r="F42" s="11" t="n"/>
@@ -1556,21 +1522,21 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr"/>
       <c r="B43" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>InterlinkingGrid</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/faqsection/faqsection</t>
+          <t>./components/InterlinkingGrid/InterlinkingGrid</t>
         </is>
       </c>
       <c r="F43" s="11" t="n"/>
@@ -1578,85 +1544,85 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr"/>
       <c r="B44" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
+          <t>TrustBlock</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>./components/TrustBlock/TrustBlock</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr"/>
+      <c r="B45" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
           <t>Footer</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>@/app/components/Header/Footer/footer</t>
         </is>
       </c>
-      <c r="F44" s="11" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>/orlando/safety-guide</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n">
+      <c r="F45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/itinerary</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>@/app/components/destination/header/header</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>RED (&gt;2 missing) — missing 8: SafetyHero, InfoSection, SafetyNarrative, ScenarioSection, SafetyTipsGrid, NeighborhoodSafetySection, EmergencyContactBlock, LinkHubGrid</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr"/>
-      <c r="B46" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="n"/>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>no NYC counterpart</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr"/>
       <c r="B47" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>FAQAccordion</t>
+          <t>BookingCTA</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -1666,7 +1632,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/faqsection/faqsection</t>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
         </is>
       </c>
       <c r="F47" s="11" t="n"/>
@@ -1674,169 +1640,169 @@
     <row r="48">
       <c r="A48" s="10" t="inlineStr"/>
       <c r="B48" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/Header/Footer/footer</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/landmark</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/header/header</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr"/>
+      <c r="B50" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
           <t>BookingCTA</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>@/app/components/destination/BookingCTA/BookingCTA</t>
         </is>
       </c>
-      <c r="F48" s="11" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr"/>
-      <c r="B49" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>@/app/components/Header/Footer/footer</t>
-        </is>
-      </c>
-      <c r="F49" s="11" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>/orlando/solo-itinerary</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>@/app/components/destination/header/header</t>
-        </is>
-      </c>
-      <c r="F50" s="15" t="inlineStr">
-        <is>
-          <t>differs — missing 1: FAQ</t>
-        </is>
-      </c>
+      <c r="F50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr"/>
       <c r="B51" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/Header/Footer/footer</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/neighborhood-guide</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/header/header</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr"/>
+      <c r="B53" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>@/app/components/destination/BookingCTA/BookingCTA</t>
         </is>
       </c>
-      <c r="F51" s="11" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr"/>
-      <c r="B52" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>@/app/components/Header/Footer/footer</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>/orlando/solo-trip-to-orlando</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="12" t="inlineStr">
-        <is>
-          <t>OrlandoNavHeader</t>
-        </is>
-      </c>
-      <c r="D53" s="13" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>./components/orlandonavheader/OrlandoNavHeader</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>RED (&gt;2 missing) — missing 10: NycNavHeader, QuickActionBar, InfoSection, SoloNycQa, SoloTripNarrative, BestNeighborhoodsGrid, SubwayAccessSection, ThreeDayItinerary, ScenarioSection, FemaleSoloTiles; extra: OrlandoNavHeader</t>
-        </is>
-      </c>
+      <c r="F53" s="11" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr"/>
       <c r="B54" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>IntroSection</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>./components/introsection/introsection</t>
         </is>
       </c>
       <c r="F54" s="11" t="n"/>
@@ -1844,21 +1810,21 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr"/>
       <c r="B55" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>HeroSection</t>
-        </is>
-      </c>
-      <c r="D55" s="13" t="inlineStr">
+          <t>CityOrganization</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>./components/herosection/HeroSection</t>
+          <t>./components/cityorganization/cityorganization</t>
         </is>
       </c>
       <c r="F55" s="11" t="n"/>
@@ -1866,21 +1832,21 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr"/>
       <c r="B56" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>NeighborhoodsByStyle</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
+          <t>./components/Neighborhoodbystyle/Neighborhoodbystyle</t>
         </is>
       </c>
       <c r="F56" s="11" t="n"/>
@@ -1888,21 +1854,21 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr"/>
       <c r="B57" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>PopularNeighborhoods</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/faqsection/faqsection</t>
+          <t>./components/PopularNeighborhood/Popularneighborhood</t>
         </is>
       </c>
       <c r="F57" s="11" t="n"/>
@@ -1910,73 +1876,65 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr"/>
       <c r="B58" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>WhereFirstTimersStay</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/Header/Footer/footer</t>
+          <t>./components/Wherefirsttimerstay/wherefirsttimestay</t>
         </is>
       </c>
       <c r="F58" s="11" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>/orlando/things-to-do</t>
-        </is>
-      </c>
+      <c r="A59" s="10" t="inlineStr"/>
       <c r="B59" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>GettingAround</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/header/header</t>
-        </is>
-      </c>
-      <c r="F59" s="15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
+          <t>./components/Gettingaround/Gettingaround</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr"/>
       <c r="B60" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+          <t>SafetyOverview</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>./components/SafetyOverview/Safetyoverview</t>
         </is>
       </c>
       <c r="F60" s="11" t="n"/>
@@ -1984,27 +1942,1079 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr"/>
       <c r="B61" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>NeighborhoodGuideCTA</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>./components/Neighborhoodguidecta/Neighborhoodguidecta</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr"/>
+      <c r="B62" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/Header/Footer/footer</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/orlando-female-solo-travel-guide</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/header/header</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr"/>
+      <c r="B64" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr"/>
+      <c r="B65" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>./components/Hero/herobanner</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr"/>
+      <c r="B66" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>InfoSection</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>./components/infosection/infosection</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr"/>
+      <c r="B67" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>FemaleSafetyNarrative</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>./components/safetynarrative/FemaleSafetyNarrative</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr"/>
+      <c r="B68" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>CoreSafetyPrinciplesGrid</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>./components/coresafetyprinciples/CoreSafetyPrinciplesGrid</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr"/>
+      <c r="B69" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>ScenarioSection</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>./components/scenariosection/scenariosection</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr"/>
+      <c r="B70" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>ScenarioFilter</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>./components/scenariocard/ScenarioFilter</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr"/>
+      <c r="B71" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>SafetySection</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>./components/safetysection/SafetySection</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr"/>
+      <c r="B72" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>MicroScenarios</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>./components/microscenarios/microscenario</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr"/>
+      <c r="B73" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>PackingEssentials</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>./components/packingessential/packingEssential</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr"/>
+      <c r="B74" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>./components/FAQAccordian/faqsection</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr"/>
+      <c r="B75" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>LinkHubGrid</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>./components/linkhubgrid/LinkHubGrid</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr"/>
+      <c r="B76" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr"/>
+      <c r="B77" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>@/app/components/Header/Footer/footer</t>
         </is>
       </c>
-      <c r="F61" s="11" t="n"/>
+      <c r="F77" s="11" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/safety-guide</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/header/header</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr"/>
+      <c r="B79" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr"/>
+      <c r="B80" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>SafetyHero</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>./components/herobanner/safetyhero</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr"/>
+      <c r="B81" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>InfoSection</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>./components/infosection/infosection</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr"/>
+      <c r="B82" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>SafetyNarrative</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>./components/safetynarrative/SafetyNarrative</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr"/>
+      <c r="B83" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>ScenarioSection</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>./components/scenariosection/scenariosection</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr"/>
+      <c r="B84" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>SafetyTipsGrid</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>./components/SafetyTips/safetytipcardgrid</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr"/>
+      <c r="B85" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>NeighborhoodSafetySection</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>./components/neighborhoodsection/neighborhoodsafetysection</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr"/>
+      <c r="B86" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>EmergencyContactBlock</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>./components/emergencycontactblock/EmergencyContactBlock</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr"/>
+      <c r="B87" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>./components/FAQAccordian/faqsection</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr"/>
+      <c r="B88" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>LinkHubGrid</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>./components/linkhubgrid/LinkHubGrid</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr"/>
+      <c r="B89" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr"/>
+      <c r="B90" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/Header/Footer/footer</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/solo-itinerary</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/header/header</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>differs — missing 1: FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr"/>
+      <c r="B92" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr"/>
+      <c r="B93" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/Header/Footer/footer</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>/orlando/solo-trip-to-orlando</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>OrlandoNavHeader</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>./components/orlandonavheader/OrlandoNavHeader</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>RED (&gt;2 missing) — missing 5: NycNavHeader, QuickActionBar, SoloNycQa, SubwayAccessSection, ScenarioSection; extra: OrlandoNavHeader</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr"/>
+      <c r="B95" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>HeroSection</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>./components/herosection/HeroSection</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr"/>
+      <c r="B96" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr"/>
+      <c r="B97" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>InfoSection</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/infosection/infosection</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr"/>
+      <c r="B98" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr"/>
+      <c r="B99" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>SoloTripNarrative</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>./components/solotripnarrative/SoloTripNarrative</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr"/>
+      <c r="B100" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>BestNeighborhoodsGrid</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/BestNeighborhoodGrid/bestneighborhoodgrid</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr"/>
+      <c r="B101" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>ThreeDayItinerary</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/itinerary/itinerary</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr"/>
+      <c r="B102" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>FemaleSoloTiles</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/Solofemaletravel/solofemaletravel</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr"/>
+      <c r="B103" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/faqsection/faqsection</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr"/>
+      <c r="B104" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/Header/Footer/footer</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>/orlando/things-to-do</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/header/header</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr"/>
+      <c r="B106" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr"/>
+      <c r="B107" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>@/app/components/Header/Footer/footer</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F61"/>
+  <autoFilter ref="A4:F107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2015,7 +3025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2028,7 +3038,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>New York City — Components by Route (in page order)</t>
+          <t>New York City — Components by Route (reference)</t>
         </is>
       </c>
     </row>
@@ -2067,7 +3077,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>/nyc</t>
         </is>
@@ -2075,7 +3085,7 @@
       <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
@@ -2096,12 +3106,12 @@
       <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>HeroSection</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2117,12 +3127,12 @@
       <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2138,12 +3148,12 @@
       <c r="B8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>PlanningIntent</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2159,12 +3169,12 @@
       <c r="B9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>WhyVisit</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2180,12 +3190,12 @@
       <c r="B10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>AttractionsHub</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2201,12 +3211,12 @@
       <c r="B11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>NeighborhoodsHub</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2222,12 +3232,12 @@
       <c r="B12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>ExperiencesHub</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2243,12 +3253,12 @@
       <c r="B13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>WhereToStay</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2264,12 +3274,12 @@
       <c r="B14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>ItinerariesPreview</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2285,12 +3295,12 @@
       <c r="B15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>DataCaptureCTA</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2306,7 +3316,7 @@
       <c r="B16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -2323,7 +3333,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>/nyc/best-areas-to-stay</t>
         </is>
@@ -2331,7 +3341,7 @@
       <c r="B17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
@@ -2352,7 +3362,7 @@
       <c r="B18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
@@ -2373,7 +3383,7 @@
       <c r="B19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Banner</t>
         </is>
@@ -2394,7 +3404,7 @@
       <c r="B20" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>SoloTripIntro</t>
         </is>
@@ -2415,7 +3425,7 @@
       <c r="B21" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>SectionSafestNeighborhoods</t>
         </is>
@@ -2436,7 +3446,7 @@
       <c r="B22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>NeighborhoodRankingCards</t>
         </is>
@@ -2457,7 +3467,7 @@
       <c r="B23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>FAQAccordion</t>
         </is>
@@ -2478,7 +3488,7 @@
       <c r="B24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -2495,7 +3505,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>/nyc/booking</t>
         </is>
@@ -2503,7 +3513,7 @@
       <c r="B25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>BookingClient</t>
         </is>
@@ -2520,7 +3530,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>/nyc/food</t>
         </is>
@@ -2528,12 +3538,12 @@
       <c r="B26" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2549,7 +3559,7 @@
       <c r="B27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
@@ -2570,7 +3580,7 @@
       <c r="B28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -2587,7 +3597,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>/nyc/group-travel</t>
         </is>
@@ -2595,12 +3605,12 @@
       <c r="B29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2616,7 +3626,7 @@
       <c r="B30" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
@@ -2637,7 +3647,7 @@
       <c r="B31" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -2654,7 +3664,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>/nyc/is-nyc-safe-at-night</t>
         </is>
@@ -2662,7 +3672,7 @@
       <c r="B32" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
@@ -2683,7 +3693,7 @@
       <c r="B33" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
@@ -2704,12 +3714,12 @@
       <c r="B34" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>HeroSafety</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2725,12 +3735,12 @@
       <c r="B35" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>SafetyMeter</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2746,12 +3756,12 @@
       <c r="B36" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>NeighborhoodSafetyGrid</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2767,12 +3777,12 @@
       <c r="B37" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>ScenarioCards</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2788,12 +3798,12 @@
       <c r="B38" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>CorePrinciples</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2809,12 +3819,12 @@
       <c r="B39" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>TransitSafety</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2830,12 +3840,12 @@
       <c r="B40" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>NeighborhoodCards</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2851,12 +3861,12 @@
       <c r="B41" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>EmergencyBlock</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2872,12 +3882,12 @@
       <c r="B42" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>FAQAccordion</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2893,12 +3903,12 @@
       <c r="B43" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C43" s="12" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>InterlinkingGrid</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2914,12 +3924,12 @@
       <c r="B44" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C44" s="12" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>TrustBlock</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2935,7 +3945,7 @@
       <c r="B45" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C45" s="12" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -2952,7 +3962,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>/nyc/landmark</t>
         </is>
@@ -2960,12 +3970,12 @@
       <c r="B46" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="12" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -2981,7 +3991,7 @@
       <c r="B47" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
@@ -3002,7 +4012,7 @@
       <c r="B48" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -3019,7 +4029,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>/nyc/neighborhood-guide</t>
         </is>
@@ -3027,7 +4037,7 @@
       <c r="B49" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
@@ -3048,7 +4058,7 @@
       <c r="B50" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
@@ -3069,12 +4079,12 @@
       <c r="B51" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>IntroSection</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3090,12 +4100,12 @@
       <c r="B52" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>CityOrganization</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3111,12 +4121,12 @@
       <c r="B53" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>NeighborhoodsByStyle</t>
         </is>
       </c>
-      <c r="D53" s="13" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3132,12 +4142,12 @@
       <c r="B54" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>PopularNeighborhoods</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3153,12 +4163,12 @@
       <c r="B55" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>WhereFirstTimersStay</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3174,12 +4184,12 @@
       <c r="B56" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>GettingAround</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3195,12 +4205,12 @@
       <c r="B57" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>SafetyOverview</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3216,12 +4226,12 @@
       <c r="B58" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C58" s="12" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>NeighborhoodGuideCTA</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3237,7 +4247,7 @@
       <c r="B59" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C59" s="12" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -3254,7 +4264,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>/nyc/nyc-female-solo-travel-guide</t>
         </is>
@@ -3262,7 +4272,7 @@
       <c r="B60" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C60" s="12" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
@@ -3283,7 +4293,7 @@
       <c r="B61" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C61" s="12" t="inlineStr">
+      <c r="C61" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
@@ -3304,12 +4314,12 @@
       <c r="B62" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>Hero</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3325,12 +4335,12 @@
       <c r="B63" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>InfoSection</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3346,12 +4356,12 @@
       <c r="B64" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C64" s="12" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>FemaleSafetyNarrative</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3367,12 +4377,12 @@
       <c r="B65" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>CoreSafetyPrinciplesGrid</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3388,12 +4398,12 @@
       <c r="B66" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C66" s="12" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>ScenarioSection</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3409,12 +4419,12 @@
       <c r="B67" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C67" s="12" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
         <is>
           <t>ScenarioFilter</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3430,12 +4440,12 @@
       <c r="B68" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C68" s="12" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>SafetySection</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3451,12 +4461,12 @@
       <c r="B69" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C69" s="14" t="inlineStr">
         <is>
           <t>MicroScenarios</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D69" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3472,12 +4482,12 @@
       <c r="B70" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>PackingEssentials</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3493,12 +4503,12 @@
       <c r="B71" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C71" s="12" t="inlineStr">
+      <c r="C71" s="14" t="inlineStr">
         <is>
           <t>FAQAccordion</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3514,12 +4524,12 @@
       <c r="B72" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>LinkHubGrid</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D72" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3535,7 +4545,7 @@
       <c r="B73" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C73" s="12" t="inlineStr">
+      <c r="C73" s="14" t="inlineStr">
         <is>
           <t>WhyTrustThisGuide</t>
         </is>
@@ -3556,7 +4566,7 @@
       <c r="B74" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C74" s="12" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -3573,7 +4583,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="14" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>/nyc/nyc-safety-guide</t>
         </is>
@@ -3581,7 +4591,7 @@
       <c r="B75" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="C75" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
@@ -3602,7 +4612,7 @@
       <c r="B76" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C76" s="12" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
@@ -3623,12 +4633,12 @@
       <c r="B77" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C77" s="12" t="inlineStr">
+      <c r="C77" s="14" t="inlineStr">
         <is>
           <t>SafetyHero</t>
         </is>
       </c>
-      <c r="D77" s="13" t="inlineStr">
+      <c r="D77" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3644,12 +4654,12 @@
       <c r="B78" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>InfoSection</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D78" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3665,12 +4675,12 @@
       <c r="B79" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C79" s="12" t="inlineStr">
+      <c r="C79" s="14" t="inlineStr">
         <is>
           <t>SafetyNarrative</t>
         </is>
       </c>
-      <c r="D79" s="13" t="inlineStr">
+      <c r="D79" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3686,12 +4696,12 @@
       <c r="B80" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C80" s="12" t="inlineStr">
+      <c r="C80" s="14" t="inlineStr">
         <is>
           <t>ScenarioSection</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3707,12 +4717,12 @@
       <c r="B81" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C81" s="12" t="inlineStr">
+      <c r="C81" s="14" t="inlineStr">
         <is>
           <t>SafetyTipsGrid</t>
         </is>
       </c>
-      <c r="D81" s="13" t="inlineStr">
+      <c r="D81" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3728,12 +4738,12 @@
       <c r="B82" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C82" s="14" t="inlineStr">
         <is>
           <t>NeighborhoodSafetySection</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3749,12 +4759,12 @@
       <c r="B83" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C83" s="12" t="inlineStr">
+      <c r="C83" s="14" t="inlineStr">
         <is>
           <t>EmergencyContactBlock</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D83" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3770,12 +4780,12 @@
       <c r="B84" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>FAQAccordion</t>
         </is>
       </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3791,12 +4801,12 @@
       <c r="B85" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="C85" s="14" t="inlineStr">
         <is>
           <t>LinkHubGrid</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="D85" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3812,7 +4822,7 @@
       <c r="B86" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C86" s="12" t="inlineStr">
+      <c r="C86" s="14" t="inlineStr">
         <is>
           <t>WhyTrustThisGuide</t>
         </is>
@@ -3833,7 +4843,7 @@
       <c r="B87" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C87" s="12" t="inlineStr">
+      <c r="C87" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -3850,7 +4860,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="14" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>/nyc/nyc-subway-map</t>
         </is>
@@ -3858,7 +4868,7 @@
       <c r="B88" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C88" s="14" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
@@ -3879,7 +4889,7 @@
       <c r="B89" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C89" s="12" t="inlineStr">
+      <c r="C89" s="14" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
@@ -3900,12 +4910,12 @@
       <c r="B90" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C90" s="12" t="inlineStr">
+      <c r="C90" s="14" t="inlineStr">
         <is>
           <t>HeroBanner</t>
         </is>
       </c>
-      <c r="D90" s="13" t="inlineStr">
+      <c r="D90" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3921,12 +4931,12 @@
       <c r="B91" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C91" s="12" t="inlineStr">
+      <c r="C91" s="14" t="inlineStr">
         <is>
           <t>IconCardGrid</t>
         </is>
       </c>
-      <c r="D91" s="13" t="inlineStr">
+      <c r="D91" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3942,12 +4952,12 @@
       <c r="B92" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C92" s="12" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
         <is>
           <t>StepList</t>
         </is>
       </c>
-      <c r="D92" s="13" t="inlineStr">
+      <c r="D92" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3963,12 +4973,12 @@
       <c r="B93" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C93" s="12" t="inlineStr">
+      <c r="C93" s="14" t="inlineStr">
         <is>
           <t>ScenarioCards</t>
         </is>
       </c>
-      <c r="D93" s="13" t="inlineStr">
+      <c r="D93" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -3984,12 +4994,12 @@
       <c r="B94" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C94" s="12" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>SafetyChecklist</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
@@ -4005,7 +5015,7 @@
       <c r="B95" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C95" s="12" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
@@ -4022,53 +5032,59 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>/nyc/nyc-subway-map/full</t>
-        </is>
-      </c>
-      <c r="B96" s="17" t="n"/>
-      <c r="C96" s="17" t="inlineStr">
-        <is>
-          <t>(none)</t>
-        </is>
-      </c>
-      <c r="D96" s="17" t="n"/>
-      <c r="E96" s="17" t="n"/>
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>/nyc/solo-itinerary</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>../../../components/Header/header</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="14" t="inlineStr">
-        <is>
-          <t>/nyc/solo-itinerary</t>
-        </is>
-      </c>
+      <c r="A97" s="10" t="inlineStr"/>
       <c r="B97" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="D97" s="13" t="inlineStr">
-        <is>
-          <t>Local</t>
+        <v>2</v>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>../../../components/Header/header</t>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr"/>
       <c r="B98" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
+        <v>3</v>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -4078,18 +5094,18 @@
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>@/app/components/faq/faq</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr"/>
       <c r="B99" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>FAQ</t>
+        <v>4</v>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>Footer</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -4099,85 +5115,85 @@
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/faq/faq</t>
+          <t>@/app/components/Header/Footer/footer</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr"/>
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>/nyc/solo-trip-to-nyc</t>
+        </is>
+      </c>
       <c r="B100" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C100" s="12" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+        <v>1</v>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>NycNavHeader</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/Header/Footer/footer</t>
+          <t>./components/nycnavheader/NycNavHeader</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="14" t="inlineStr">
-        <is>
-          <t>/nyc/solo-trip-to-nyc</t>
-        </is>
-      </c>
+      <c r="A101" s="10" t="inlineStr"/>
       <c r="B101" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" s="12" t="inlineStr">
-        <is>
-          <t>NycNavHeader</t>
-        </is>
-      </c>
-      <c r="D101" s="13" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>HeroSection</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>./components/nycnavheader/NycNavHeader</t>
+          <t>./components/herosection/HeroSection</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr"/>
       <c r="B102" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C102" s="12" t="inlineStr">
-        <is>
-          <t>HeroSection</t>
-        </is>
-      </c>
-      <c r="D102" s="13" t="inlineStr">
-        <is>
-          <t>Local</t>
+        <v>3</v>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>./components/herosection/HeroSection</t>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr"/>
       <c r="B103" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
+        <v>4</v>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>QuickActionBar</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -4187,18 +5203,18 @@
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>@/app/components/quickactionbar/quickactionbar</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr"/>
       <c r="B104" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>QuickActionBar</t>
+        <v>5</v>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>InfoSection</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -4208,18 +5224,18 @@
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/quickactionbar/quickactionbar</t>
+          <t>@/app/components/infosection/infosection</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr"/>
       <c r="B105" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>InfoSection</t>
+        <v>6</v>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -4229,18 +5245,18 @@
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/infosection/infosection</t>
+          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr"/>
       <c r="B106" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C106" s="12" t="inlineStr">
-        <is>
-          <t>WhyTrustThisGuide</t>
+        <v>7</v>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>SoloNycQa</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -4250,60 +5266,60 @@
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/whytrustitem/whytrustthisguide</t>
+          <t>@/app/components/destination/solotriptonyc/aisnippet/cardqanda</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr"/>
       <c r="B107" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C107" s="12" t="inlineStr">
-        <is>
-          <t>SoloNycQa</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+        <v>8</v>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>SoloTripNarrative</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/solotriptonyc/aisnippet/cardqanda</t>
+          <t>./components/solotripnarrative/SoloTripNarrative</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr"/>
       <c r="B108" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>SoloTripNarrative</t>
-        </is>
-      </c>
-      <c r="D108" s="13" t="inlineStr">
-        <is>
-          <t>Local</t>
+        <v>9</v>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>BestNeighborhoodsGrid</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>./components/solotripnarrative/SoloTripNarrative</t>
+          <t>@/app/components/BestNeighborhoodGrid/bestneighborhoodgrid</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr"/>
       <c r="B109" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>BestNeighborhoodsGrid</t>
+        <v>10</v>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>SubwayAccessSection</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -4313,18 +5329,18 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/BestNeighborhoodGrid/bestneighborhoodgrid</t>
+          <t>@/app/components/destination/subwayaccess/subwayaccess</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr"/>
       <c r="B110" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>SubwayAccessSection</t>
+        <v>11</v>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>ThreeDayItinerary</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -4334,18 +5350,18 @@
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/subwayaccess/subwayaccess</t>
+          <t>@/app/components/itinerary/itinerary</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr"/>
       <c r="B111" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C111" s="12" t="inlineStr">
-        <is>
-          <t>ThreeDayItinerary</t>
+        <v>12</v>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>ScenarioSection</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -4355,18 +5371,18 @@
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/itinerary/itinerary</t>
+          <t>@/app/components/destination/scenariocard/scenariosection</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr"/>
       <c r="B112" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C112" s="12" t="inlineStr">
-        <is>
-          <t>ScenarioSection</t>
+        <v>13</v>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>FemaleSoloTiles</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -4376,18 +5392,18 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/scenariocard/scenariosection</t>
+          <t>@/app/components/Solofemaletravel/solofemaletravel</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="10" t="inlineStr"/>
       <c r="B113" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>FemaleSoloTiles</t>
+        <v>14</v>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -4397,18 +5413,18 @@
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/Solofemaletravel/solofemaletravel</t>
+          <t>@/app/components/destination/faqsection/faqsection</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr"/>
       <c r="B114" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C114" s="12" t="inlineStr">
-        <is>
-          <t>FAQAccordion</t>
+        <v>15</v>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>Footer</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -4418,18 +5434,22 @@
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/faqsection/faqsection</t>
+          <t>@/app/components/Header/Footer/footer</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="10" t="inlineStr"/>
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>/nyc/subway-safety-guide</t>
+        </is>
+      </c>
       <c r="B115" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C115" s="12" t="inlineStr">
-        <is>
-          <t>Footer</t>
+        <v>1</v>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>Header</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -4439,22 +5459,18 @@
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/Header/Footer/footer</t>
+          <t>@/app/components/destination/header/header</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="14" t="inlineStr">
-        <is>
-          <t>/nyc/subway-safety-guide</t>
-        </is>
-      </c>
+      <c r="A116" s="10" t="inlineStr"/>
       <c r="B116" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>Header</t>
+        <v>2</v>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -4464,312 +5480,316 @@
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/header/header</t>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr"/>
       <c r="B117" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C117" s="12" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
+        <v>3</v>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Local</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
+          <t>./components/Hero/Hero</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr"/>
       <c r="B118" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C118" s="12" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="D118" s="13" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>./components/Hero/Hero</t>
+          <t>./components/whytrustthisguide/whytrustthisguide</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr"/>
       <c r="B119" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C119" s="12" t="inlineStr">
-        <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="D119" s="13" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>CorePrinciples</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>./components/whytrustthisguide/whytrustthisguide</t>
+          <t>./components/coreprinciples/coreprinciples</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr"/>
       <c r="B120" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>CorePrinciples</t>
-        </is>
-      </c>
-      <c r="D120" s="13" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>SubwayBasics</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>./components/coreprinciples/coreprinciples</t>
+          <t>./components/subwaybasics/SubwayBasics</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr"/>
       <c r="B121" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C121" s="12" t="inlineStr">
-        <is>
-          <t>SubwayBasics</t>
-        </is>
-      </c>
-      <c r="D121" s="13" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>PersonaBlock</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>./components/subwaybasics/SubwayBasics</t>
+          <t>./components/PersonaBlock/PersonalBlock</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr"/>
       <c r="B122" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>PersonaBlock</t>
-        </is>
-      </c>
-      <c r="D122" s="13" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>ScenarioList</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>./components/PersonaBlock/PersonalBlock</t>
+          <t>./components/ScenarioList/ScenarioList</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr"/>
       <c r="B123" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C123" s="12" t="inlineStr">
-        <is>
-          <t>ScenarioList</t>
-        </is>
-      </c>
-      <c r="D123" s="13" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>NeighborhoodNotes</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>./components/ScenarioList/ScenarioList</t>
+          <t>./components/neighborhood/neighborhood</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr"/>
       <c r="B124" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C124" s="12" t="inlineStr">
-        <is>
-          <t>NeighborhoodNotes</t>
-        </is>
-      </c>
-      <c r="D124" s="13" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>./components/neighborhood/neighborhood</t>
+          <t>./components/FAQ/FAQ</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr"/>
       <c r="B125" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C125" s="12" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="D125" s="13" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>./components/FAQ/FAQ</t>
+          <t>./components/checklist/checklist</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr"/>
       <c r="B126" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>Checklist</t>
-        </is>
-      </c>
-      <c r="D126" s="13" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>EmergencyPlaybook</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>./components/checklist/checklist</t>
+          <t>./components/EmergencyPlaybook/EmergencyPlaybook</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr"/>
       <c r="B127" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C127" s="12" t="inlineStr">
-        <is>
-          <t>EmergencyPlaybook</t>
-        </is>
-      </c>
-      <c r="D127" s="13" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>ToolsAndApps</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>./components/EmergencyPlaybook/EmergencyPlaybook</t>
+          <t>./components/Toolsandapps/Toolsandapps</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr"/>
       <c r="B128" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>ToolsAndApps</t>
-        </is>
-      </c>
-      <c r="D128" s="13" t="inlineStr">
+        <v>14</v>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>Etiquette</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>./components/Toolsandapps/Toolsandapps</t>
+          <t>./components/Etiquette/Etiquette</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr"/>
       <c r="B129" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>Etiquette</t>
-        </is>
-      </c>
-      <c r="D129" s="13" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>InternalLinks</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>./components/Etiquette/Etiquette</t>
+          <t>./components/Interlink/Interlink</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr"/>
       <c r="B130" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C130" s="12" t="inlineStr">
-        <is>
-          <t>InternalLinks</t>
-        </is>
-      </c>
-      <c r="D130" s="13" t="inlineStr">
-        <is>
-          <t>Local</t>
+        <v>16</v>
+      </c>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Shared</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>./components/Interlink/Interlink</t>
+          <t>../../../../app/components/Header/Footer/footer</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="10" t="inlineStr"/>
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>/nyc/things-to-do</t>
+        </is>
+      </c>
       <c r="B131" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C131" s="12" t="inlineStr">
-        <is>
-          <t>Footer</t>
+        <v>1</v>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>Header</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
@@ -4779,22 +5799,18 @@
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>../../../../app/components/Header/Footer/footer</t>
+          <t>@/app/components/destination/header/header</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="14" t="inlineStr">
-        <is>
-          <t>/nyc/things-to-do</t>
-        </is>
-      </c>
+      <c r="A132" s="10" t="inlineStr"/>
       <c r="B132" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>Header</t>
+        <v>2</v>
+      </c>
+      <c r="C132" s="14" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
         </is>
       </c>
       <c r="D132" s="7" t="inlineStr">
@@ -4804,18 +5820,18 @@
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/header/header</t>
+          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr"/>
       <c r="B133" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C133" s="12" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
+        <v>3</v>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>Footer</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
@@ -4825,33 +5841,12 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>@/app/components/destination/BookingCTA/BookingCTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="10" t="inlineStr"/>
-      <c r="B134" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C134" s="12" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="D134" s="7" t="inlineStr">
-        <is>
-          <t>Shared</t>
-        </is>
-      </c>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
           <t>../../../../app/components/Header/Footer/footer</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E134"/>
+  <autoFilter ref="A4:E133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4862,7 +5857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4902,1532 +5897,1480 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>/orlando</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Existing</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr"/>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr"/>
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Existing</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="inlineStr"/>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr"/>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>HeroSection</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr"/>
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="21" t="inlineStr"/>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>OrlandoPlanningQuiz</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Existing</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr"/>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr"/>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>PlanningIntent</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr"/>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>WhyVisit</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr"/>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>AttractionsHub</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr"/>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>NeighborhoodsHub</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr"/>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>ExperiencesHub</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr"/>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>WhereToStay</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr"/>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>ItinerariesPreview</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr"/>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>DataCaptureCTA</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/best-areas-to-stay</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr"/>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr"/>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr"/>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>SoloTripIntro</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr"/>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>SectionSafestNeighborhoods</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr"/>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>NeighborhoodRankingCards</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/bookings</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>BookingClient</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/food</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr"/>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr"/>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/group-travel</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr"/>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr"/>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/is-orlando-safe-at-night</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr"/>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr"/>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>HeroSafety</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr"/>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>SafetyMeter</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr"/>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>NeighborhoodSafetyGrid</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr"/>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>ScenarioCards</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr"/>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>CorePrinciples</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr"/>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>TransitSafety</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr"/>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>NeighborhoodCards</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr"/>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>EmergencyBlock</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr"/>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr"/>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>InterlinkingGrid</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr"/>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>TrustBlock</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr"/>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/itinerary</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr"/>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr"/>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/landmark</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr"/>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr"/>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/neighborhood-guide</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr"/>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr"/>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>IntroSection</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="inlineStr"/>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>CityOrganization</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="19" t="inlineStr"/>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>NeighborhoodsByStyle</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr"/>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>PopularNeighborhoods</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="inlineStr"/>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>WhereFirstTimersStay</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr"/>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>GettingAround</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr"/>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>SafetyOverview</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr"/>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>NeighborhoodGuideCTA</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="19" t="inlineStr"/>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/orlando-female-solo-travel-guide</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="19" t="inlineStr"/>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="inlineStr"/>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="19" t="inlineStr"/>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>InfoSection</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="19" t="inlineStr"/>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>FemaleSafetyNarrative</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="19" t="inlineStr"/>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>CoreSafetyPrinciplesGrid</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="19" t="inlineStr"/>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>ScenarioSection</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="inlineStr"/>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>ScenarioFilter</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19" t="inlineStr"/>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>SafetySection</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="19" t="inlineStr"/>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>MicroScenarios</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="19" t="inlineStr"/>
+      <c r="B73" s="17" t="inlineStr">
+        <is>
+          <t>PackingEssentials</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="19" t="inlineStr"/>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="19" t="inlineStr"/>
+      <c r="B75" s="17" t="inlineStr">
+        <is>
+          <t>LinkHubGrid</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="19" t="inlineStr"/>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="19" t="inlineStr"/>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/safety-guide</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="19" t="inlineStr"/>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="19" t="inlineStr"/>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>SafetyHero</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="19" t="inlineStr"/>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>InfoSection</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="19" t="inlineStr"/>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>SafetyNarrative</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="19" t="inlineStr"/>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>ScenarioSection</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="inlineStr"/>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>SafetyTipsGrid</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="19" t="inlineStr"/>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>NeighborhoodSafetySection</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="19" t="inlineStr"/>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>EmergencyContactBlock</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="19" t="inlineStr"/>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="19" t="inlineStr"/>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>LinkHubGrid</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="19" t="inlineStr"/>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="19" t="inlineStr"/>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/solo-itinerary</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="19" t="inlineStr"/>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="19" t="inlineStr"/>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="19" t="inlineStr"/>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="C94" s="21" t="inlineStr">
+        <is>
+          <t>MISSING (in NYC, not Orlando)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/solo-trip-to-orlando</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>OrlandoNavHeader</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="19" t="inlineStr"/>
+      <c r="B96" s="17" t="inlineStr">
         <is>
           <t>HeroSection</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="19" t="inlineStr"/>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>BookingCTA</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="19" t="inlineStr"/>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>InfoSection</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="19" t="inlineStr"/>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>WhyTrustThisGuide</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="19" t="inlineStr"/>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>SoloTripNarrative</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="inlineStr"/>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>BestNeighborhoodsGrid</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="19" t="inlineStr"/>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>ThreeDayItinerary</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="19" t="inlineStr"/>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>FemaleSoloTiles</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="19" t="inlineStr"/>
+      <c r="B104" s="17" t="inlineStr">
+        <is>
+          <t>FAQAccordion</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="19" t="inlineStr"/>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="inlineStr"/>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>NycNavHeader</t>
+        </is>
+      </c>
+      <c r="C106" s="21" t="inlineStr">
         <is>
           <t>MISSING (in NYC, not Orlando)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr"/>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>PlanningIntent</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="19" t="inlineStr"/>
+      <c r="B107" s="20" t="inlineStr">
+        <is>
+          <t>QuickActionBar</t>
+        </is>
+      </c>
+      <c r="C107" s="21" t="inlineStr">
         <is>
           <t>MISSING (in NYC, not Orlando)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="21" t="inlineStr"/>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>WhyVisit</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="19" t="inlineStr"/>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>SoloNycQa</t>
+        </is>
+      </c>
+      <c r="C108" s="21" t="inlineStr">
         <is>
           <t>MISSING (in NYC, not Orlando)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr"/>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>AttractionsHub</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="19" t="inlineStr"/>
+      <c r="B109" s="20" t="inlineStr">
+        <is>
+          <t>SubwayAccessSection</t>
+        </is>
+      </c>
+      <c r="C109" s="21" t="inlineStr">
         <is>
           <t>MISSING (in NYC, not Orlando)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="21" t="inlineStr"/>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>NeighborhoodsHub</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="19" t="inlineStr"/>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>ScenarioSection</t>
+        </is>
+      </c>
+      <c r="C110" s="21" t="inlineStr">
         <is>
           <t>MISSING (in NYC, not Orlando)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr"/>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>ExperiencesHub</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="inlineStr"/>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>WhereToStay</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr"/>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>ItinerariesPreview</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr"/>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>DataCaptureCTA</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/best-areas-to-stay</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="16" t="inlineStr">
+        <is>
+          <t>/orlando/things-to-do</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="inlineStr"/>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="19" t="inlineStr"/>
+      <c r="B112" s="17" t="inlineStr">
         <is>
           <t>BookingCTA</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr"/>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>Banner</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="inlineStr"/>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>SoloTripIntro</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="inlineStr"/>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>SectionSafestNeighborhoods</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="inlineStr"/>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>NeighborhoodRankingCards</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr"/>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr"/>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="19" t="inlineStr"/>
+      <c r="B113" s="17" t="inlineStr">
         <is>
           <t>Footer</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/bookings</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>BookingClient</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/food</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr"/>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr"/>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/group-travel</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr"/>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr"/>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/is-orlando-safe-at-night</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="21" t="inlineStr"/>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="21" t="inlineStr"/>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr"/>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr"/>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr"/>
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>HeroSafety</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr"/>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>SafetyMeter</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr"/>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>NeighborhoodSafetyGrid</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr"/>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>ScenarioCards</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="21" t="inlineStr"/>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>CorePrinciples</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="21" t="inlineStr"/>
-      <c r="B43" s="22" t="inlineStr">
-        <is>
-          <t>TransitSafety</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="21" t="inlineStr"/>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>NeighborhoodCards</t>
-        </is>
-      </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="21" t="inlineStr"/>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>EmergencyBlock</t>
-        </is>
-      </c>
-      <c r="C45" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="21" t="inlineStr"/>
-      <c r="B46" s="22" t="inlineStr">
-        <is>
-          <t>InterlinkingGrid</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="21" t="inlineStr"/>
-      <c r="B47" s="22" t="inlineStr">
-        <is>
-          <t>TrustBlock</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/itinerary</t>
-        </is>
-      </c>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C48" s="20" t="inlineStr">
-        <is>
-          <t>Existing (no NYC counterpart to compare)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="21" t="inlineStr"/>
-      <c r="B49" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="inlineStr"/>
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C50" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/landmark</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="21" t="inlineStr"/>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C52" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="21" t="inlineStr"/>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/neighborhood-guide</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C54" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="21" t="inlineStr"/>
-      <c r="B55" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="21" t="inlineStr"/>
-      <c r="B56" s="19" t="inlineStr">
-        <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="21" t="inlineStr"/>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="21" t="inlineStr"/>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="21" t="inlineStr"/>
-      <c r="B59" s="22" t="inlineStr">
-        <is>
-          <t>IntroSection</t>
-        </is>
-      </c>
-      <c r="C59" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="21" t="inlineStr"/>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>CityOrganization</t>
-        </is>
-      </c>
-      <c r="C60" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="21" t="inlineStr"/>
-      <c r="B61" s="22" t="inlineStr">
-        <is>
-          <t>NeighborhoodsByStyle</t>
-        </is>
-      </c>
-      <c r="C61" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="21" t="inlineStr"/>
-      <c r="B62" s="22" t="inlineStr">
-        <is>
-          <t>PopularNeighborhoods</t>
-        </is>
-      </c>
-      <c r="C62" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="21" t="inlineStr"/>
-      <c r="B63" s="22" t="inlineStr">
-        <is>
-          <t>WhereFirstTimersStay</t>
-        </is>
-      </c>
-      <c r="C63" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="21" t="inlineStr"/>
-      <c r="B64" s="22" t="inlineStr">
-        <is>
-          <t>GettingAround</t>
-        </is>
-      </c>
-      <c r="C64" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="21" t="inlineStr"/>
-      <c r="B65" s="22" t="inlineStr">
-        <is>
-          <t>SafetyOverview</t>
-        </is>
-      </c>
-      <c r="C65" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="21" t="inlineStr"/>
-      <c r="B66" s="22" t="inlineStr">
-        <is>
-          <t>NeighborhoodGuideCTA</t>
-        </is>
-      </c>
-      <c r="C66" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/orlando-female-solo-travel-guide</t>
-        </is>
-      </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C67" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="21" t="inlineStr"/>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C68" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="21" t="inlineStr"/>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="C69" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="21" t="inlineStr"/>
-      <c r="B70" s="19" t="inlineStr">
-        <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="C70" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="21" t="inlineStr"/>
-      <c r="B71" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="21" t="inlineStr"/>
-      <c r="B72" s="22" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="C72" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="21" t="inlineStr"/>
-      <c r="B73" s="22" t="inlineStr">
-        <is>
-          <t>InfoSection</t>
-        </is>
-      </c>
-      <c r="C73" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="21" t="inlineStr"/>
-      <c r="B74" s="22" t="inlineStr">
-        <is>
-          <t>FemaleSafetyNarrative</t>
-        </is>
-      </c>
-      <c r="C74" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="21" t="inlineStr"/>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>CoreSafetyPrinciplesGrid</t>
-        </is>
-      </c>
-      <c r="C75" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="21" t="inlineStr"/>
-      <c r="B76" s="22" t="inlineStr">
-        <is>
-          <t>ScenarioSection</t>
-        </is>
-      </c>
-      <c r="C76" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="21" t="inlineStr"/>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>ScenarioFilter</t>
-        </is>
-      </c>
-      <c r="C77" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="21" t="inlineStr"/>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>SafetySection</t>
-        </is>
-      </c>
-      <c r="C78" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="21" t="inlineStr"/>
-      <c r="B79" s="22" t="inlineStr">
-        <is>
-          <t>MicroScenarios</t>
-        </is>
-      </c>
-      <c r="C79" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="21" t="inlineStr"/>
-      <c r="B80" s="22" t="inlineStr">
-        <is>
-          <t>PackingEssentials</t>
-        </is>
-      </c>
-      <c r="C80" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="21" t="inlineStr"/>
-      <c r="B81" s="22" t="inlineStr">
-        <is>
-          <t>LinkHubGrid</t>
-        </is>
-      </c>
-      <c r="C81" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/safety-guide</t>
-        </is>
-      </c>
-      <c r="B82" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C82" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="21" t="inlineStr"/>
-      <c r="B83" s="19" t="inlineStr">
-        <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="C83" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="21" t="inlineStr"/>
-      <c r="B84" s="19" t="inlineStr">
-        <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="C84" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="21" t="inlineStr"/>
-      <c r="B85" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C85" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="21" t="inlineStr"/>
-      <c r="B86" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C86" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="21" t="inlineStr"/>
-      <c r="B87" s="22" t="inlineStr">
-        <is>
-          <t>SafetyHero</t>
-        </is>
-      </c>
-      <c r="C87" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="21" t="inlineStr"/>
-      <c r="B88" s="22" t="inlineStr">
-        <is>
-          <t>InfoSection</t>
-        </is>
-      </c>
-      <c r="C88" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="21" t="inlineStr"/>
-      <c r="B89" s="22" t="inlineStr">
-        <is>
-          <t>SafetyNarrative</t>
-        </is>
-      </c>
-      <c r="C89" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="21" t="inlineStr"/>
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>ScenarioSection</t>
-        </is>
-      </c>
-      <c r="C90" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="21" t="inlineStr"/>
-      <c r="B91" s="22" t="inlineStr">
-        <is>
-          <t>SafetyTipsGrid</t>
-        </is>
-      </c>
-      <c r="C91" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="21" t="inlineStr"/>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>NeighborhoodSafetySection</t>
-        </is>
-      </c>
-      <c r="C92" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="21" t="inlineStr"/>
-      <c r="B93" s="22" t="inlineStr">
-        <is>
-          <t>EmergencyContactBlock</t>
-        </is>
-      </c>
-      <c r="C93" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="21" t="inlineStr"/>
-      <c r="B94" s="22" t="inlineStr">
-        <is>
-          <t>LinkHubGrid</t>
-        </is>
-      </c>
-      <c r="C94" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/solo-itinerary</t>
-        </is>
-      </c>
-      <c r="B95" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C95" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="21" t="inlineStr"/>
-      <c r="B96" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C96" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="21" t="inlineStr"/>
-      <c r="B97" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C97" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="21" t="inlineStr"/>
-      <c r="B98" s="22" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-      <c r="C98" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/solo-trip-to-orlando</t>
-        </is>
-      </c>
-      <c r="B99" s="19" t="inlineStr">
-        <is>
-          <t>OrlandoNavHeader</t>
-        </is>
-      </c>
-      <c r="C99" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="21" t="inlineStr"/>
-      <c r="B100" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C100" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="21" t="inlineStr"/>
-      <c r="B101" s="19" t="inlineStr">
-        <is>
-          <t>HeroSection</t>
-        </is>
-      </c>
-      <c r="C101" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="21" t="inlineStr"/>
-      <c r="B102" s="19" t="inlineStr">
-        <is>
-          <t>WhyTrustThisGuide</t>
-        </is>
-      </c>
-      <c r="C102" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="21" t="inlineStr"/>
-      <c r="B103" s="19" t="inlineStr">
-        <is>
-          <t>FAQAccordion</t>
-        </is>
-      </c>
-      <c r="C103" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="21" t="inlineStr"/>
-      <c r="B104" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C104" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="21" t="inlineStr"/>
-      <c r="B105" s="22" t="inlineStr">
-        <is>
-          <t>NycNavHeader</t>
-        </is>
-      </c>
-      <c r="C105" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="21" t="inlineStr"/>
-      <c r="B106" s="22" t="inlineStr">
-        <is>
-          <t>QuickActionBar</t>
-        </is>
-      </c>
-      <c r="C106" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="21" t="inlineStr"/>
-      <c r="B107" s="22" t="inlineStr">
-        <is>
-          <t>InfoSection</t>
-        </is>
-      </c>
-      <c r="C107" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="21" t="inlineStr"/>
-      <c r="B108" s="22" t="inlineStr">
-        <is>
-          <t>SoloNycQa</t>
-        </is>
-      </c>
-      <c r="C108" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="21" t="inlineStr"/>
-      <c r="B109" s="22" t="inlineStr">
-        <is>
-          <t>SoloTripNarrative</t>
-        </is>
-      </c>
-      <c r="C109" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="21" t="inlineStr"/>
-      <c r="B110" s="22" t="inlineStr">
-        <is>
-          <t>BestNeighborhoodsGrid</t>
-        </is>
-      </c>
-      <c r="C110" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="21" t="inlineStr"/>
-      <c r="B111" s="22" t="inlineStr">
-        <is>
-          <t>SubwayAccessSection</t>
-        </is>
-      </c>
-      <c r="C111" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="21" t="inlineStr"/>
-      <c r="B112" s="22" t="inlineStr">
-        <is>
-          <t>ThreeDayItinerary</t>
-        </is>
-      </c>
-      <c r="C112" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="21" t="inlineStr"/>
-      <c r="B113" s="22" t="inlineStr">
-        <is>
-          <t>ScenarioSection</t>
-        </is>
-      </c>
-      <c r="C113" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="21" t="inlineStr"/>
-      <c r="B114" s="22" t="inlineStr">
-        <is>
-          <t>FemaleSoloTiles</t>
-        </is>
-      </c>
-      <c r="C114" s="23" t="inlineStr">
-        <is>
-          <t>MISSING (in NYC, not Orlando)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="18" t="inlineStr">
-        <is>
-          <t>/orlando/things-to-do</t>
-        </is>
-      </c>
-      <c r="B115" s="19" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="C115" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="21" t="inlineStr"/>
-      <c r="B116" s="19" t="inlineStr">
-        <is>
-          <t>BookingCTA</t>
-        </is>
-      </c>
-      <c r="C116" s="20" t="inlineStr">
-        <is>
-          <t>Existing</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="21" t="inlineStr"/>
-      <c r="B117" s="19" t="inlineStr">
-        <is>
-          <t>Footer</t>
-        </is>
-      </c>
-      <c r="C117" s="20" t="inlineStr">
+      <c r="C113" s="18" t="inlineStr">
         <is>
           <t>Existing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C117"/>
+  <autoFilter ref="A4:C113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>